--- a/results/SamChigome/analysis/n_10/AllData.xlsx
+++ b/results/SamChigome/analysis/n_10/AllData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owuor\owProjects\StructuralGT\results\SamChigome\analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owuor\owProjects\StructuralGT\results\SamChigome\analysis\n_10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B9FEAD-44E5-401B-A4B4-A7F40F0ABCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD345C3C-8067-4842-921F-AD6DC480F469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="14" xr2:uid="{E8351862-8131-4AC1-82A9-213539580791}"/>
+    <workbookView xWindow="360" yWindow="375" windowWidth="27690" windowHeight="10455" firstSheet="9" activeTab="14" xr2:uid="{E8351862-8131-4AC1-82A9-213539580791}"/>
   </bookViews>
   <sheets>
     <sheet name="SGT Descriptors" sheetId="2" r:id="rId1"/>
@@ -4887,8 +4887,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B89027AB-5D9D-4421-B80B-99DB9E634340}" name="Table6" displayName="Table6" ref="A5:B9" totalsRowShown="0">
-  <autoFilter ref="A5:B9" xr:uid="{B89027AB-5D9D-4421-B80B-99DB9E634340}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B89027AB-5D9D-4421-B80B-99DB9E634340}" name="Table6" displayName="Table6" ref="A2:B6" totalsRowShown="0">
+  <autoFilter ref="A2:B6" xr:uid="{B89027AB-5D9D-4421-B80B-99DB9E634340}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{70364C0B-1320-4A7E-AD30-25F8414086FE}" name="a"/>
     <tableColumn id="2" xr3:uid="{AEDFE533-B065-41FB-A636-6D5C56171853}" name="k"/>
@@ -6402,46 +6402,46 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20DC337-6F2B-4C6F-A1A5-B5E5DC0F7BCC}">
-  <dimension ref="A5:B9"/>
+  <dimension ref="A2:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2.77</v>
+      </c>
+      <c r="B3">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2.41</v>
+      </c>
+      <c r="B4">
+        <v>0.95</v>
+      </c>
+    </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
+      <c r="A5">
+        <v>2.76</v>
+      </c>
+      <c r="B5">
+        <v>0.96</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="B6">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2.41</v>
-      </c>
-      <c r="B7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2.76</v>
-      </c>
-      <c r="B8">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2.75</v>
-      </c>
-      <c r="B9">
         <v>0.95</v>
       </c>
     </row>

--- a/results/SamChigome/analysis/n_10/AllData.xlsx
+++ b/results/SamChigome/analysis/n_10/AllData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owuor\owProjects\StructuralGT\results\SamChigome\analysis\n_10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792F782A-4680-4824-A245-A14FBF855761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2942B487-AB49-4F2C-BCA6-E5B4AC2870E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="375" windowWidth="27690" windowHeight="10455" activeTab="14" xr2:uid="{E8351862-8131-4AC1-82A9-213539580791}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{E8351862-8131-4AC1-82A9-213539580791}"/>
   </bookViews>
   <sheets>
     <sheet name="SGT Descriptors" sheetId="2" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="36">
   <si>
     <t>CC</t>
   </si>
@@ -1175,6 +1175,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1182,7 +1183,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1793,6 +1793,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1800,7 +1801,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2602,6 +2602,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2609,7 +2610,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11387,7 +11387,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{908D8F90-1399-4559-8642-02E0AC650D8E}">
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -12092,31 +12092,31 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22">
-        <v>665</v>
+        <v>65</v>
       </c>
       <c r="C22">
-        <v>8165</v>
+        <v>55.3</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>2.2313423961572751</v>
       </c>
       <c r="E22">
-        <v>5.5600000000000007E-3</v>
+        <v>7.1235999999999994E-2</v>
       </c>
       <c r="F22">
-        <v>2.8912057932946778E-19</v>
+        <v>4.7470201647396059E-3</v>
       </c>
       <c r="G22">
-        <v>3.9119561890726868</v>
+        <v>1.7427251313046981</v>
       </c>
       <c r="H22">
-        <v>-2.254925208417943</v>
+        <v>-1.1473004747604389</v>
       </c>
       <c r="I22">
-        <v>-2.2680279442499329</v>
+        <v>-1.15188756303448</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -12124,28 +12124,28 @@
         <v>5</v>
       </c>
       <c r="B23">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="C23">
-        <v>55.3</v>
+        <v>211.6</v>
       </c>
       <c r="D23">
-        <v>2.2313423961572751</v>
+        <v>4.3772137256478576</v>
       </c>
       <c r="E23">
-        <v>7.1235999999999994E-2</v>
+        <v>3.4527000000000009E-2</v>
       </c>
       <c r="F23">
-        <v>4.7470201647396059E-3</v>
+        <v>8.7654631620037293E-4</v>
       </c>
       <c r="G23">
-        <v>1.7427251313046981</v>
+        <v>2.3255156633631482</v>
       </c>
       <c r="H23">
-        <v>-1.1473004747604389</v>
+        <v>-1.461841155216919</v>
       </c>
       <c r="I23">
-        <v>-1.15188756303448</v>
+        <v>-1.460781329376569</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -12153,28 +12153,28 @@
         <v>5</v>
       </c>
       <c r="B24">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="C24">
-        <v>211.6</v>
+        <v>478.7</v>
       </c>
       <c r="D24">
-        <v>4.3772137256478576</v>
+        <v>5.587784295526566</v>
       </c>
       <c r="E24">
-        <v>3.4527000000000009E-2</v>
+        <v>2.2575000000000001E-2</v>
       </c>
       <c r="F24">
-        <v>8.7654631620037293E-4</v>
+        <v>3.8453507281159983E-4</v>
       </c>
       <c r="G24">
-        <v>2.3255156633631482</v>
+        <v>2.680063427481949</v>
       </c>
       <c r="H24">
-        <v>-1.461841155216919</v>
+        <v>-1.646372241014457</v>
       </c>
       <c r="I24">
-        <v>-1.460781329376569</v>
+        <v>-1.648700638600761</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -12182,28 +12182,28 @@
         <v>5</v>
       </c>
       <c r="B25">
-        <v>196</v>
+        <v>262</v>
       </c>
       <c r="C25">
-        <v>478.7</v>
+        <v>872.7</v>
       </c>
       <c r="D25">
-        <v>5.587784295526566</v>
+        <v>5.3417641696769467</v>
       </c>
       <c r="E25">
-        <v>2.2575000000000001E-2</v>
+        <v>1.6201E-2</v>
       </c>
       <c r="F25">
-        <v>3.8453507281159983E-4</v>
+        <v>1.4882092146827571E-4</v>
       </c>
       <c r="G25">
-        <v>2.680063427481949</v>
+        <v>2.940864975966722</v>
       </c>
       <c r="H25">
-        <v>-1.646372241014457</v>
+        <v>-1.7904581779833999</v>
       </c>
       <c r="I25">
-        <v>-1.648700638600761</v>
+        <v>-1.7869320753654721</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -12211,28 +12211,28 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="C26">
-        <v>872.7</v>
+        <v>1350.5</v>
       </c>
       <c r="D26">
-        <v>5.3417641696769467</v>
+        <v>5.814254514170802</v>
       </c>
       <c r="E26">
-        <v>1.6201E-2</v>
+        <v>1.286E-2</v>
       </c>
       <c r="F26">
-        <v>1.4882092146827571E-4</v>
+        <v>1.2406091693644339E-4</v>
       </c>
       <c r="G26">
-        <v>2.940864975966722</v>
+        <v>3.1304945885234701</v>
       </c>
       <c r="H26">
-        <v>-1.7904581779833999</v>
+        <v>-1.890759031411797</v>
       </c>
       <c r="I26">
-        <v>-1.7869320753654721</v>
+        <v>-1.887440580583897</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -12240,28 +12240,28 @@
         <v>5</v>
       </c>
       <c r="B27">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="C27">
-        <v>1350.5</v>
+        <v>1956.9</v>
       </c>
       <c r="D27">
-        <v>5.814254514170802</v>
+        <v>8.1846061467719871</v>
       </c>
       <c r="E27">
-        <v>1.286E-2</v>
+        <v>1.0566000000000001E-2</v>
       </c>
       <c r="F27">
-        <v>1.2406091693644339E-4</v>
+        <v>8.9134106204577431E-5</v>
       </c>
       <c r="G27">
-        <v>3.1304945885234701</v>
+        <v>3.2915686332421501</v>
       </c>
       <c r="H27">
-        <v>-1.890759031411797</v>
+        <v>-1.97608939364908</v>
       </c>
       <c r="I27">
-        <v>-1.887440580583897</v>
+        <v>-1.972813910444577</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -12269,28 +12269,28 @@
         <v>5</v>
       </c>
       <c r="B28">
-        <v>393</v>
+        <v>458</v>
       </c>
       <c r="C28">
-        <v>1956.9</v>
+        <v>2651.9</v>
       </c>
       <c r="D28">
-        <v>8.1846061467719871</v>
+        <v>8.6106523175270127</v>
       </c>
       <c r="E28">
-        <v>1.0566000000000001E-2</v>
+        <v>9.0380000000000009E-3</v>
       </c>
       <c r="F28">
-        <v>8.9134106204577431E-5</v>
+        <v>6.0291882630343361E-5</v>
       </c>
       <c r="G28">
-        <v>3.2915686332421501</v>
+        <v>3.423557143312292</v>
       </c>
       <c r="H28">
-        <v>-1.97608939364908</v>
+        <v>-2.0439276630048169</v>
       </c>
       <c r="I28">
-        <v>-1.972813910444577</v>
+        <v>-2.0427711690936552</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -12298,28 +12298,28 @@
         <v>5</v>
       </c>
       <c r="B29">
-        <v>458</v>
+        <v>524</v>
       </c>
       <c r="C29">
-        <v>2651.9</v>
+        <v>3473</v>
       </c>
       <c r="D29">
-        <v>8.6106523175270127</v>
+        <v>6.7396010432533933</v>
       </c>
       <c r="E29">
-        <v>9.0380000000000009E-3</v>
+        <v>7.8090000000000008E-3</v>
       </c>
       <c r="F29">
-        <v>6.0291882630343361E-5</v>
+        <v>3.2810906045940768E-5</v>
       </c>
       <c r="G29">
-        <v>3.423557143312292</v>
+        <v>3.5407047833107619</v>
       </c>
       <c r="H29">
-        <v>-2.0439276630048169</v>
+        <v>-2.1074045771711019</v>
       </c>
       <c r="I29">
-        <v>-2.0427711690936552</v>
+        <v>-2.1048623901184769</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -12327,28 +12327,28 @@
         <v>5</v>
       </c>
       <c r="B30">
-        <v>524</v>
+        <v>589</v>
       </c>
       <c r="C30">
-        <v>3473</v>
+        <v>4398.1000000000004</v>
       </c>
       <c r="D30">
-        <v>6.7396010432533933</v>
+        <v>2.3449709782615411</v>
       </c>
       <c r="E30">
-        <v>7.8090000000000008E-3</v>
+        <v>6.8970000000000004E-3</v>
       </c>
       <c r="F30">
-        <v>3.2810906045940768E-5</v>
+        <v>1.8800118202938078E-5</v>
       </c>
       <c r="G30">
-        <v>3.5407047833107619</v>
+        <v>3.6432650997301961</v>
       </c>
       <c r="H30">
-        <v>-2.1074045771711019</v>
+        <v>-2.1613397740110591</v>
       </c>
       <c r="I30">
-        <v>-2.1048623901184769</v>
+        <v>-2.1592219595921591</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -12356,57 +12356,57 @@
         <v>5</v>
       </c>
       <c r="B31">
-        <v>589</v>
+        <v>655</v>
       </c>
       <c r="C31">
-        <v>4398.1000000000004</v>
+        <v>5425.8</v>
       </c>
       <c r="D31">
-        <v>2.3449709782615411</v>
+        <v>7.5037768268163907</v>
       </c>
       <c r="E31">
-        <v>6.8970000000000004E-3</v>
+        <v>6.1460000000000004E-3</v>
       </c>
       <c r="F31">
-        <v>1.8800118202938078E-5</v>
+        <v>6.3595946761129686E-6</v>
       </c>
       <c r="G31">
-        <v>3.6432650997301961</v>
+        <v>3.734463781224838</v>
       </c>
       <c r="H31">
-        <v>-2.1613397740110591</v>
+        <v>-2.211407444079641</v>
       </c>
       <c r="I31">
-        <v>-2.1592219595921591</v>
+        <v>-2.2075595743313889</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B32">
-        <v>655</v>
+        <v>65</v>
       </c>
       <c r="C32">
-        <v>5425.8</v>
+        <v>49.8</v>
       </c>
       <c r="D32">
-        <v>7.5037768268163907</v>
+        <v>1.2092238098144701</v>
       </c>
       <c r="E32">
-        <v>6.1460000000000004E-3</v>
+        <v>6.3321000000000002E-2</v>
       </c>
       <c r="F32">
-        <v>6.3595946761129686E-6</v>
+        <v>1.91857032998822E-3</v>
       </c>
       <c r="G32">
-        <v>3.734463781224838</v>
+        <v>1.697229342759718</v>
       </c>
       <c r="H32">
-        <v>-2.211407444079641</v>
+        <v>-1.1984522351386051</v>
       </c>
       <c r="I32">
-        <v>-2.2075595743313889</v>
+        <v>-1.172239015000931</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -12414,28 +12414,28 @@
         <v>6</v>
       </c>
       <c r="B33">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="C33">
-        <v>49.8</v>
+        <v>213.4</v>
       </c>
       <c r="D33">
-        <v>1.2092238098144701</v>
+        <v>4.0830271994086829</v>
       </c>
       <c r="E33">
-        <v>6.3321000000000002E-2</v>
+        <v>3.3064999999999997E-2</v>
       </c>
       <c r="F33">
-        <v>1.91857032998822E-3</v>
+        <v>1.2767347675483221E-3</v>
       </c>
       <c r="G33">
-        <v>1.697229342759718</v>
+        <v>2.3291944150884509</v>
       </c>
       <c r="H33">
-        <v>-1.1984522351386051</v>
+        <v>-1.4806314729600001</v>
       </c>
       <c r="I33">
-        <v>-1.172239015000931</v>
+        <v>-1.5042845632925339</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -12443,28 +12443,28 @@
         <v>6</v>
       </c>
       <c r="B34">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="C34">
-        <v>213.4</v>
+        <v>470.4</v>
       </c>
       <c r="D34">
-        <v>4.0830271994086829</v>
+        <v>5.1901616331071789</v>
       </c>
       <c r="E34">
-        <v>3.3064999999999997E-2</v>
+        <v>2.1065E-2</v>
       </c>
       <c r="F34">
-        <v>1.2767347675483221E-3</v>
+        <v>3.8763743082651073E-4</v>
       </c>
       <c r="G34">
-        <v>2.3291944150884509</v>
+        <v>2.6724673130680818</v>
       </c>
       <c r="H34">
-        <v>-1.4806314729600001</v>
+        <v>-1.676438536537133</v>
       </c>
       <c r="I34">
-        <v>-1.5042845632925339</v>
+        <v>-1.68464617284048</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -12472,28 +12472,28 @@
         <v>6</v>
       </c>
       <c r="B35">
-        <v>196</v>
+        <v>262</v>
       </c>
       <c r="C35">
-        <v>470.4</v>
+        <v>836.4</v>
       </c>
       <c r="D35">
-        <v>5.1901616331071789</v>
+        <v>8.5481641953761685</v>
       </c>
       <c r="E35">
-        <v>2.1065E-2</v>
+        <v>1.6246E-2</v>
       </c>
       <c r="F35">
-        <v>3.8763743082651073E-4</v>
+        <v>4.5558558166630138E-4</v>
       </c>
       <c r="G35">
-        <v>2.6724673130680818</v>
+        <v>2.9224140241456338</v>
       </c>
       <c r="H35">
-        <v>-1.676438536537133</v>
+        <v>-1.7892535511016741</v>
       </c>
       <c r="I35">
-        <v>-1.68464617284048</v>
+        <v>-1.815972564689327</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -12501,28 +12501,28 @@
         <v>6</v>
       </c>
       <c r="B36">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="C36">
-        <v>836.4</v>
+        <v>1306.5</v>
       </c>
       <c r="D36">
-        <v>8.5481641953761685</v>
+        <v>6.0429021725216323</v>
       </c>
       <c r="E36">
-        <v>1.6246E-2</v>
+        <v>1.2062E-2</v>
       </c>
       <c r="F36">
-        <v>4.5558558166630138E-4</v>
+        <v>1.5347674452864549E-4</v>
       </c>
       <c r="G36">
-        <v>2.9224140241456338</v>
+        <v>3.1161094140633439</v>
       </c>
       <c r="H36">
-        <v>-1.7892535511016741</v>
+        <v>-1.9185806758650661</v>
       </c>
       <c r="I36">
-        <v>-1.815972564689327</v>
+        <v>-1.9177435244510499</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -12530,28 +12530,28 @@
         <v>6</v>
       </c>
       <c r="B37">
-        <v>327</v>
+        <v>393</v>
       </c>
       <c r="C37">
-        <v>1306.5</v>
+        <v>1873.9</v>
       </c>
       <c r="D37">
-        <v>6.0429021725216323</v>
+        <v>10.574024777727731</v>
       </c>
       <c r="E37">
-        <v>1.2062E-2</v>
+        <v>9.8149999999999991E-3</v>
       </c>
       <c r="F37">
-        <v>1.5347674452864549E-4</v>
+        <v>7.5103632106280678E-5</v>
       </c>
       <c r="G37">
-        <v>3.1161094140633439</v>
+        <v>3.2727464112011901</v>
       </c>
       <c r="H37">
-        <v>-1.9185806758650661</v>
+        <v>-2.008109696063975</v>
       </c>
       <c r="I37">
-        <v>-1.9177435244510499</v>
+        <v>-2.0000433537845481</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -12559,28 +12559,28 @@
         <v>6</v>
       </c>
       <c r="B38">
-        <v>393</v>
+        <v>458</v>
       </c>
       <c r="C38">
-        <v>1873.9</v>
+        <v>2520.6</v>
       </c>
       <c r="D38">
-        <v>10.574024777727731</v>
+        <v>6.49307323229917</v>
       </c>
       <c r="E38">
-        <v>9.8149999999999991E-3</v>
+        <v>8.4430000000000009E-3</v>
       </c>
       <c r="F38">
-        <v>7.5103632106280678E-5</v>
+        <v>6.4876806333234388E-5</v>
       </c>
       <c r="G38">
-        <v>3.2727464112011901</v>
+        <v>3.4015039319216358</v>
       </c>
       <c r="H38">
-        <v>-2.008109696063975</v>
+        <v>-2.0735032107267801</v>
       </c>
       <c r="I38">
-        <v>-2.0000433537845481</v>
+        <v>-2.0676948165572382</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -12588,28 +12588,28 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>458</v>
+        <v>524</v>
       </c>
       <c r="C39">
-        <v>2520.6</v>
+        <v>3300.4</v>
       </c>
       <c r="D39">
-        <v>6.49307323229917</v>
+        <v>12.533687938246</v>
       </c>
       <c r="E39">
-        <v>8.4430000000000009E-3</v>
+        <v>7.3020000000000003E-3</v>
       </c>
       <c r="F39">
-        <v>6.4876806333234388E-5</v>
+        <v>2.7800879282657391E-5</v>
       </c>
       <c r="G39">
-        <v>3.4015039319216358</v>
+        <v>3.5185665784431182</v>
       </c>
       <c r="H39">
-        <v>-2.0735032107267801</v>
+        <v>-2.1365581713862909</v>
       </c>
       <c r="I39">
-        <v>-2.0676948165572382</v>
+        <v>-2.1292015870270982</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -12617,28 +12617,28 @@
         <v>6</v>
       </c>
       <c r="B40">
-        <v>524</v>
+        <v>589</v>
       </c>
       <c r="C40">
-        <v>3300.4</v>
+        <v>4173.8</v>
       </c>
       <c r="D40">
-        <v>12.533687938246</v>
+        <v>9.9808705921767036</v>
       </c>
       <c r="E40">
-        <v>7.3020000000000003E-3</v>
+        <v>6.431000000000001E-3</v>
       </c>
       <c r="F40">
-        <v>2.7800879282657391E-5</v>
+        <v>1.361779881054366E-5</v>
       </c>
       <c r="G40">
-        <v>3.5185665784431182</v>
+        <v>3.620531634720475</v>
       </c>
       <c r="H40">
-        <v>-2.1365581713862909</v>
+        <v>-2.191721490417232</v>
       </c>
       <c r="I40">
-        <v>-2.1292015870270982</v>
+        <v>-2.1827758184216259</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -12646,56 +12646,27 @@
         <v>6</v>
       </c>
       <c r="B41">
-        <v>589</v>
+        <v>655</v>
       </c>
       <c r="C41">
-        <v>4173.8</v>
+        <v>5203.6000000000004</v>
       </c>
       <c r="D41">
-        <v>9.9808705921767036</v>
+        <v>9.5174693181655279</v>
       </c>
       <c r="E41">
-        <v>6.431000000000001E-3</v>
+        <v>5.7330000000000002E-3</v>
       </c>
       <c r="F41">
-        <v>1.361779881054366E-5</v>
+        <v>8.6986589004666455E-6</v>
       </c>
       <c r="G41">
-        <v>3.620531634720475</v>
+        <v>3.7163039050168698</v>
       </c>
       <c r="H41">
-        <v>-2.191721490417232</v>
+        <v>-2.2416180582253249</v>
       </c>
       <c r="I41">
-        <v>-2.1827758184216259</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42">
-        <v>655</v>
-      </c>
-      <c r="C42">
-        <v>5203.6000000000004</v>
-      </c>
-      <c r="D42">
-        <v>9.5174693181655279</v>
-      </c>
-      <c r="E42">
-        <v>5.7330000000000002E-3</v>
-      </c>
-      <c r="F42">
-        <v>8.6986589004666455E-6</v>
-      </c>
-      <c r="G42">
-        <v>3.7163039050168698</v>
-      </c>
-      <c r="H42">
-        <v>-2.2416180582253249</v>
-      </c>
-      <c r="I42">
         <v>-2.233096251296999</v>
       </c>
     </row>
